--- a/out/Attention-mamba2_repeat_1_000006.xlsx
+++ b/out/Attention-mamba2_repeat_1_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.581772643840161</v>
+        <v>3.996122136721797</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.1562253596518723</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>-1.31935606704792e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.01698092984976127</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.03399441767155367</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.003923906093737067</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.0130438301953536</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.0130438301953536</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>0.01300708642913972</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.1128847963586313</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>0.2390014591602818</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.02159923383643674</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>0.1691503972061777</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.03783310649458993</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>0.2232279641372454</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.02071878588571975</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>0.2267998195622389</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.00855522440327813</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.0002221295996836852</v>
+        <v>0.2231718958245069</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.2605387606726226</v>
+        <v>0.01066028094634972</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5215804819213596</v>
+        <v>0.235937988592505</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.1747706733836651</v>
+        <v>0.006416841554896468</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6102881635158881</v>
+        <v>0.2381056027215752</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.1556729544031905</v>
+        <v>0.004876382754238524</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.7467504974081923</v>
+        <v>0.2414411298386073</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.06632679724838325</v>
+        <v>0.002154847917098913</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.7235564015537084</v>
+        <v>0.2408692019079276</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.05905966517237759</v>
+        <v>0.001707581821199297</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.829132276861946</v>
+        <v>4.596122136721797</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.7753159652031665</v>
+        <v>0.2421314193351213</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.0292421029268216</v>
+        <v>0.0008455032895237159</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.1562253596518723</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.7746852842664619</v>
+        <v>0.2421112399622563</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.01744913615259895</v>
+        <v>0.000489564126757022</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.1562253596518723</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7803210416531204</v>
+        <v>0.2422444157103396</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.008723968159358655</v>
+        <v>0.000242282063378511</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.7803034691659065</v>
+        <v>0.2422391078274778</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.004298277933719643</v>
+        <v>0.0001157352228200315</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.7801721806505011</v>
+        <v>0.2422310169424913</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.002549767110865139</v>
+        <v>6.509070833595748e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7809683315139366</v>
+        <v>0.2422458631855596</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.00079251727928659</v>
+        <v>1.955167125369099e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.7800012270106994</v>
+        <v>0.2422164780483809</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0003967578038692074</v>
+        <v>6.228955736355216e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.7800016194983688</v>
+        <v>0.2422116161368874</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0002165969308555446</v>
+        <v>2.338588390325519e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.780039828512949</v>
+        <v>0.242207810813799</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.0001016936185379291</v>
+        <v>-2.629819553036738e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.780026372222998</v>
+        <v>0.2422025795182146</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>6.29003573329541e-05</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.7800509561594205</v>
+        <v>0.2421986552318635</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.55637255026519e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.7800366121355894</v>
+        <v>0.2421983231285403</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>1.29424116614095e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7800369138645127</v>
+        <v>0.2421987036635981</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>3.373746146054129e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7800335002489914</v>
+        <v>0.2421989319846327</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>7.621708635915141e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7800288519032152</v>
+        <v>0.2421990219292827</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>-2.975818632750635e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.7800221330033776</v>
+        <v>0.2421981639956979</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.7800223613244123</v>
+        <v>0.2421983923167326</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.7800215656602005</v>
+        <v>0.2421975966525208</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.7800216279295736</v>
+        <v>0.2421976589218939</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.7800216556048505</v>
+        <v>0.2421976865971708</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7800218078188738</v>
+        <v>0.2421978388111941</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.7800214618779121</v>
+        <v>0.2421974928702323</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.7800215379849237</v>
+        <v>0.242197568977244</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7800217040365853</v>
+        <v>0.2421977350289056</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.7800220638151854</v>
+        <v>0.2421980948075056</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.780022084571643</v>
+        <v>0.2421981155639633</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.7800221883539316</v>
+        <v>0.2421982193462518</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7800224166749662</v>
+        <v>0.2421984476672865</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.78002229213622</v>
+        <v>0.2421983231285403</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.829132276861946</v>
+        <v>4.596122136721797</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.7800223198114968</v>
+        <v>0.2421983508038172</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.1562253596518723</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.7800223751620509</v>
+        <v>0.2421984061543711</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.1562253596518723</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.7800226380771815</v>
+        <v>0.2421986690695018</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7800225550513508</v>
+        <v>0.242198586043671</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.829132276861946</v>
+        <v>4.596122136721797</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.780022347486774</v>
+        <v>0.2421983784790943</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.829132276861946</v>
+        <v>4.596122136721797</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7800223613244123</v>
+        <v>0.2421983923167326</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.829132276861946</v>
+        <v>4.596122136721797</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7800224997007971</v>
+        <v>0.2421985306931173</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.229132276861946</v>
+        <v>4.596122136721797</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7800222160292084</v>
+        <v>0.2421982470215287</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.229132276861946</v>
+        <v>4.596122136721797</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7800220430587277</v>
+        <v>0.2421980740510479</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.1562253596518723</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7800219392764391</v>
+        <v>0.2421979702687594</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.229132276861946</v>
+        <v>4.596122136721797</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.780022084571643</v>
+        <v>0.2421981155639633</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.229132276861946</v>
+        <v>3.996122136721797</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7800223267303162</v>
+        <v>0.2421983577226365</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.229132276861946</v>
+        <v>4.596122136721797</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7800221537598353</v>
+        <v>0.2421981847521556</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.229132276861946</v>
+        <v>4.596122136721797</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.7800218562506084</v>
+        <v>0.2421978872429286</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7800218424129698</v>
+        <v>0.2421978734052901</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7800214757155506</v>
+        <v>0.2421975067078709</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.7800214757155506</v>
+        <v>0.2421975067078709</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.7800214134461775</v>
+        <v>0.2421974444384978</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.7800213096638891</v>
+        <v>0.2421973406562093</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7800211366934082</v>
+        <v>0.2421971676857285</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.7800211851251428</v>
+        <v>0.2421972161174631</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7800208253465427</v>
+        <v>0.242196856338863</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.7800207838336274</v>
+        <v>0.2421968148259476</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7800208391841811</v>
+        <v>0.2421968701765013</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.780020894534735</v>
+        <v>0.2421969255270553</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.7800209360476504</v>
+        <v>0.2421969670399707</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7800206662137004</v>
+        <v>0.2421966972060206</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.7800207215642543</v>
+        <v>0.2421967525565745</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.7800208668594582</v>
+        <v>0.2421968978517784</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.7800208322653619</v>
+        <v>0.2421968632576822</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.7800208184277234</v>
+        <v>0.2421968494200436</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.7800209083723736</v>
+        <v>0.2421969393646938</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7800212266380582</v>
+        <v>0.2421972576303785</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7800210467487581</v>
+        <v>0.2421970777410783</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7800210882616735</v>
+        <v>0.2421971192539937</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7800209014535542</v>
+        <v>0.2421969324458744</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7800209706417467</v>
+        <v>0.2421970016340669</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7800207699959888</v>
+        <v>0.2421968009883091</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7800208115089042</v>
+        <v>0.2421968425012245</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-4.268085246219792e-06</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.7562253596518723</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7800208391841811</v>
+        <v>0.2421968701765013</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_1_000006.xlsx
+++ b/out/Attention-mamba2_repeat_1_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,17 +36712,17 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>-6.578175903181546e-06</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.00547412273440972</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>-0.005480700910312939</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>-0.005480700910312939</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>-0.005503136366716237</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.0689264119029738</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>0.1324872612198615</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.01318835437543924</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>0.08983664844685491</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.02310065344691399</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>0.1228560657951376</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.01265040199849463</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.07643725961562864</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>0.1250366614532985</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.005221938623170979</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.07643725961562864</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.0002221295996836852</v>
+        <v>0.1228195271504431</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.2605387606726226</v>
+        <v>0.006507002726855846</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9817726438401608</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5215804819213596</v>
+        <v>0.1306122955682173</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.1747706733836651</v>
+        <v>0.003915454513182425</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.829132276861946</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6102881635158881</v>
+        <v>0.1319338501569841</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.1556729544031905</v>
+        <v>0.00297557195041653</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.829132276861946</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.7467504974081923</v>
+        <v>0.1339688155515415</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.06632679724838325</v>
+        <v>0.001314112414416554</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.829132276861946</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.7235564015537084</v>
+        <v>0.13361756817666</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.05905966517237759</v>
+        <v>0.001041717902500307</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.829132276861946</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.7753159652031665</v>
+        <v>0.134386511630913</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.0292421029268216</v>
+        <v>0.0005128064145041447</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.829132276861946</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.7746852842664619</v>
+        <v>0.1343722493150933</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.01744913615259895</v>
+        <v>0.0002975568775454723</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.829132276861946</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7803210416531204</v>
+        <v>0.1344517803609795</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.008723968159358655</v>
+        <v>0.0001462784387727361</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156287</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.7803034691659065</v>
+        <v>0.1344465920091111</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.004298277933719643</v>
+        <v>6.974085222192426e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.7801721806505011</v>
+        <v>0.1344397000195123</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.002549767110865139</v>
+        <v>3.838948611273558e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7809683315139366</v>
+        <v>0.1344466988227666</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.00079251727928659</v>
+        <v>8.391820683831448e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.7800012270106994</v>
+        <v>0.1344272908277735</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0003967578038692074</v>
+        <v>1.73737344181313e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156287</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.7800016194983688</v>
+        <v>0.1344223792159329</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0002165969308555446</v>
+        <v>-1.076077397829875e-07</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.229132276861946</v>
+        <v>-0.2764372596156287</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.780039828512949</v>
+        <v>0.1344181756672075</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.0001016936185379291</v>
+        <v>-2.629819553036738e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156287</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.780026372222998</v>
+        <v>0.1344130204786346</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>6.29003573329541e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.7800509561594205</v>
+        <v>0.1344135601465348</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.55637255026519e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.7800366121355894</v>
+        <v>0.1344132280432116</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>1.29424116614095e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156287</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7800369138645127</v>
+        <v>0.1344136085782694</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>3.373746146054129e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.07643725961562864</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7800335002489914</v>
+        <v>0.1344138368993041</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>7.621708635915141e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9817726438401608</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7800288519032152</v>
+        <v>0.134413926843954</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>-2.975818632750635e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.829132276861946</v>
+        <v>-0.07643725961562864</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.7800221330033776</v>
+        <v>0.1344130689103692</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-0.07643725961562864</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.7800223613244123</v>
+        <v>0.1344132972314039</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-0.07643725961562864</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.7800215656602005</v>
+        <v>0.1344125015671921</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.829132276861946</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.7800216279295736</v>
+        <v>0.1344125638365652</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.829132276861946</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.7800216556048505</v>
+        <v>0.1344125915118421</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9817726438401608</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7800218078188738</v>
+        <v>0.1344127437258654</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.829132276861946</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.7800214618779121</v>
+        <v>0.1344123977849037</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.829132276861946</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.7800215379849237</v>
+        <v>0.1344124738919153</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.829132276861946</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7800217040365853</v>
+        <v>0.1344126399435769</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.829132276861946</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.7800220638151854</v>
+        <v>0.1344129997221769</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-0.07643725961562864</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.780022084571643</v>
+        <v>0.1344130204786346</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156287</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.7800221883539316</v>
+        <v>0.1344131242609231</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.229132276861946</v>
+        <v>0.3660552936877102</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7800224166749662</v>
+        <v>0.1344133525819578</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.78002229213622</v>
+        <v>0.1344132280432116</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.829132276861946</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.7800223198114968</v>
+        <v>0.1344132557184885</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.829132276861946</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.7800223751620509</v>
+        <v>0.1344133110690424</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.829132276861946</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.7800226380771815</v>
+        <v>0.1344135739841731</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.829132276861946</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7800225550513508</v>
+        <v>0.1344134909583423</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.829132276861946</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.780022347486774</v>
+        <v>0.1344132833937656</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.829132276861946</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7800223613244123</v>
+        <v>0.1344132972314039</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.829132276861946</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7800224997007971</v>
+        <v>0.1344134356077886</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.229132276861946</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7800222160292084</v>
+        <v>0.1344131519362</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7800220430587277</v>
+        <v>0.1344129789657192</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7800219392764391</v>
+        <v>0.1344128751834307</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.780022084571643</v>
+        <v>0.1344130204786346</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7800223267303162</v>
+        <v>0.1344132626373079</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7800221537598353</v>
+        <v>0.1344130896668269</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.7800218562506084</v>
+        <v>0.1344127921575999</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7800218424129698</v>
+        <v>0.1344127783199614</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7800214757155506</v>
+        <v>0.1344124116225422</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.7800214757155506</v>
+        <v>0.1344124116225422</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.7800214134461775</v>
+        <v>0.1344123493531691</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.7800213096638891</v>
+        <v>0.1344122455708806</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7800211366934082</v>
+        <v>0.1344120726003998</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.7800211851251428</v>
+        <v>0.1344121210321344</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7800208253465427</v>
+        <v>0.1344117612535344</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.7800207838336274</v>
+        <v>0.1344117197406189</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7800208391841811</v>
+        <v>0.1344117750911727</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.780020894534735</v>
+        <v>0.1344118304417266</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.7800209360476504</v>
+        <v>0.134411871954642</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7800206662137004</v>
+        <v>0.1344116021206919</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.7800207215642543</v>
+        <v>0.1344116574712459</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.7800208668594582</v>
+        <v>0.1344118027664498</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.7800208322653619</v>
+        <v>0.1344117681723535</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.7800208184277234</v>
+        <v>0.134411754334715</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.229132276861946</v>
+        <v>0.3660552936877102</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.7800209083723736</v>
+        <v>0.1344118442793651</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.581772643840161</v>
+        <v>0.3660552936877102</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7800212266380582</v>
+        <v>0.1344121625450498</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.229132276861946</v>
+        <v>0.3660552936877102</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7800210467487581</v>
+        <v>0.1344119826557497</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.229132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7800210882616735</v>
+        <v>0.134412024168665</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.829132276861946</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7800209014535542</v>
+        <v>0.1344118373605458</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.829132276861946</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7800209706417467</v>
+        <v>0.1344119065487382</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.829132276861946</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7800207699959888</v>
+        <v>0.1344117059029804</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.829132276861946</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7800208115089042</v>
+        <v>0.1344117474158958</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-4.268085246219792e-06</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.829132276861946</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7800208391841811</v>
+        <v>0.1344117750911727</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_1_000006.xlsx
+++ b/out/Attention-mamba2_repeat_1_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.1368551254272461</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.1374592334032059</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.1638771295547485</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.2221213132143021</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.1454996913671494</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.1779671162366867</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.06639079749584198</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.1937233954668045</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.2017845958471298</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.1319743692874908</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.07692889869213104</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.03562032803893089</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9189298129189676</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.1020895838737488</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9189298129189676</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.04797064885497093</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9189298129189676</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.04467331245541573</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.9189298129189676</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.0409458763897419</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.9189298129189676</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.06864552944898605</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9189298129189676</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.1061566174030304</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9189298129189676</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.2107341289520264</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.1020998135209084</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.09389030933380127</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.16</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.04673570394515991</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.16</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.0547872930765152</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9189298129189676</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.1563673913478851</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.9189298129189676</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.06013930588960648</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.2194398790597916</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.5581631064414978</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.4216891229152679</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.2161143869161606</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.1971127986907959</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.07239572703838348</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.9189298129189676</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.0360049307346344</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9189298129189676</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.06221456080675125</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9189298129189676</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.4693469107151031</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.9189298129189676</v>
+        <v>0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.2300769537687302</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.1986175030469894</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.3091815114021301</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.1165608540177345</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.1853837072849274</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.4154267013072968</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.6120970845222473</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.5395327210426331</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.3282089829444885</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,17 +36712,17 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.2262930423021317</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-6.578175903181546e-06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.00547412273440972</v>
+        <v>0</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>StopLoss</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.2573507726192474</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.005480700910312939</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.3160260915756226</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.005480700910312939</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.2320465445518494</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.9189298129189676</v>
+        <v>0.16</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.005503136366716237</v>
+        <v>-0.0001134836890086299</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.0689264119029738</v>
+        <v>0.3486462734059427</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.01053029671311378</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9189298129189676</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.1324872612198615</v>
+        <v>0.6978736245261032</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01318835437543924</v>
+        <v>0.06670953599077314</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.09699477255344391</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9189298129189676</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.08983664844685491</v>
+        <v>0.4821374414511765</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.02310065344691399</v>
+        <v>0.1168480788927817</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.04654038324952126</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9189298129189676</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.1228560657951376</v>
+        <v>0.6491570750943663</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.01265040199849463</v>
+        <v>0.06399049843487115</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.07642298191785812</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.07643725961562864</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.1250366614532985</v>
+        <v>0.6601888416391501</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.005221938623170979</v>
+        <v>0.02642900776561955</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.02751102298498154</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.07643725961562864</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.1228195271504431</v>
+        <v>0.6489892767460235</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.006507002726855846</v>
+        <v>0.03292778527124096</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.01615172997117043</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.1306122955682173</v>
+        <v>0.6884212571697563</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.003915454513182425</v>
+        <v>0.01982737068570714</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.009855702519416809</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.1319338501569841</v>
+        <v>0.6951248869962326</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.00297557195041653</v>
+        <v>0.01507392729345747</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.01748639345169067</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.208547846991049</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.1339688155515415</v>
+        <v>0.7054371030044824</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.001314112414416554</v>
+        <v>0.006663669507098629</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.05911973863840103</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.208547846991049</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.13361756817666</v>
+        <v>0.7036814689519501</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.001041717902500307</v>
+        <v>0.005286600384206369</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.04587084427475929</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.208547846991049</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.134386511630913</v>
+        <v>0.7075900135154941</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.0005128064145041447</v>
+        <v>0.002619052796206994</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.04805872961878777</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.208547846991049</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.1343722493150933</v>
+        <v>0.7075381599292262</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.0002975568775454723</v>
+        <v>0.001522330391455509</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.03247519582509995</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.1344517803609795</v>
+        <v>0.7079598791512484</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0001462784387727361</v>
+        <v>0.0007572105953549397</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0617130920290947</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.2764372596156287</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1344465920091111</v>
+        <v>0.7079539301476039</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>6.974085222192426e-05</v>
+        <v>0.000371578909272003</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.03017359226942062</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.16</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.1344397000195123</v>
+        <v>0.7079393628366827</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>3.838948611273558e-05</v>
+        <v>0.0002152850833415806</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.0329170860350132</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.1344466988227666</v>
+        <v>0.7079952798378195</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>8.391820683831448e-06</v>
+        <v>6.865501376107297e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.01381964981555939</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.16</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.1344272908277735</v>
+        <v>0.7079171244262832</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>1.73737344181313e-06</v>
+        <v>3.093265835633669e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.01743665337562561</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.2764372596156287</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.1344223792159329</v>
+        <v>0.707912535866699</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>-1.076077397829875e-07</v>
+        <v>1.456956904086805e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.004714787006378174</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.2764372596156287</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.1344181756672075</v>
+        <v>0.7079109223175547</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>-2.629819553036738e-06</v>
+        <v>4.480721787853046e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.004543937742710114</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.2764372596156287</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.1344130204786346</v>
+        <v>0.7079052254562513</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.03661102801561356</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9189298129189676</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.1344135601465348</v>
+        <v>0.7079029165514493</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.005476668477058411</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9189298129189676</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.1344132280432116</v>
+        <v>0.7078969170178526</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.01681473106145859</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.2764372596156287</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.1344136085782694</v>
+        <v>0.7078926744076987</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.008164249360561371</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.07643725961562864</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.1344138368993041</v>
+        <v>0.7078929027287334</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.005340218544006348</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.134413926843954</v>
+        <v>0.7078929926733833</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.004920072853565216</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.07643725961562864</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.1344130689103692</v>
+        <v>0.7078921347397985</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.02400253713130951</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.07643725961562864</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.1344132972314039</v>
+        <v>0.7078923630608331</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.02922547608613968</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.07643725961562864</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.1344125015671921</v>
+        <v>0.7078915673966214</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.01793196797370911</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.5660552936877102</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.1344125638365652</v>
+        <v>0.7078916296659945</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.01214399188756943</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.1344125915118421</v>
+        <v>0.7078916573412714</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.002599172294139862</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.1344127437258654</v>
+        <v>0.7078918095552947</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.01746876537799835</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.1344123977849037</v>
+        <v>0.707891463614333</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.01904160529375076</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.208547846991049</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.1344124738919153</v>
+        <v>0.7078915397213446</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.02050766348838806</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.208547846991049</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.1344126399435769</v>
+        <v>0.7078917057730062</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.006058566272258759</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.5660552936877102</v>
+        <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.1344129997221769</v>
+        <v>0.7078920655516062</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.01457304507493973</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.07643725961562864</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.1344130204786346</v>
+        <v>0.707892086308064</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.01799774914979935</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.2764372596156287</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.1344131242609231</v>
+        <v>0.7078921900903524</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.01617438346147537</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.3660552936877102</v>
+        <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.1344133525819578</v>
+        <v>0.7078924184113872</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.02054236829280853</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.008547846991049</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.1344132280432116</v>
+        <v>0.707892293872641</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.04445857554674149</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.208547846991049</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.1344132557184885</v>
+        <v>0.7078923215479178</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.009290814399719238</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.208547846991049</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.1344133110690424</v>
+        <v>0.7078923768984717</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.01537223905324936</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.208547846991049</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.1344135739841731</v>
+        <v>0.7078926398136024</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.01627351343631744</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.208547846991049</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.1344134909583423</v>
+        <v>0.7078925567877716</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.01941335946321487</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.208547846991049</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.1344132833937656</v>
+        <v>0.7078923492231949</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.01986905932426453</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.208547846991049</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.1344132972314039</v>
+        <v>0.7078923630608331</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.02017711102962494</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.208547846991049</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.1344134356077886</v>
+        <v>0.7078925014372179</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.02129106968641281</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.208547846991049</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.1344131519362</v>
+        <v>0.7078922177656293</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.04842314869165421</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.008547846991049</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.1344129789657192</v>
+        <v>0.7078920447951486</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.02052116394042969</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.008547846991049</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.1344128751834307</v>
+        <v>0.70789194101286</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.02212964743375778</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.008547846991049</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.1344130204786346</v>
+        <v>0.707892086308064</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.04404269903898239</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.008547846991049</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.1344132626373079</v>
+        <v>0.7078923284667372</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.02440916001796722</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.008547846991049</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.1344130896668269</v>
+        <v>0.7078921554962562</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.04737485945224762</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.008547846991049</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.1344127921575999</v>
+        <v>0.7078918579870292</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.02588031440973282</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.008547846991049</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.1344127783199614</v>
+        <v>0.7078918441493907</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.05062063038349152</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.008547846991049</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.1344124116225422</v>
+        <v>0.7078914774519715</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.02063741534948349</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.008547846991049</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.1344124116225422</v>
+        <v>0.7078914774519715</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.01149188727140427</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.008547846991049</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.1344123493531691</v>
+        <v>0.7078914151825983</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.0496564656496048</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.008547846991049</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.1344122455708806</v>
+        <v>0.7078913114003099</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.03551651537418365</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.008547846991049</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.1344120726003998</v>
+        <v>0.7078911384298292</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.0306030735373497</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.008547846991049</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.1344121210321344</v>
+        <v>0.7078911868615637</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.03239016234874725</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.008547846991049</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.1344117612535344</v>
+        <v>0.7078908270829637</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.05111902952194214</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.008547846991049</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.1344117197406189</v>
+        <v>0.7078907855700483</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.03704218566417694</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.008547846991049</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.1344117750911727</v>
+        <v>0.7078908409206019</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.04967382550239563</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.008547846991049</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.1344118304417266</v>
+        <v>0.7078908962711559</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.05203325301408768</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.008547846991049</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.134411871954642</v>
+        <v>0.7078909377840713</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.04724203050136566</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.008547846991049</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1344116021206919</v>
+        <v>0.7078906679501212</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.04793474078178406</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.008547846991049</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.1344116574712459</v>
+        <v>0.7078907233006752</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.04894070327281952</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.008547846991049</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1344118027664498</v>
+        <v>0.707890868595879</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.04723411053419113</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.008547846991049</v>
+        <v>-0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.1344117681723535</v>
+        <v>0.7078908340017828</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.04628936201334</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.008547846991049</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.134411754334715</v>
+        <v>0.7078908201641443</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.02758223563432693</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.3660552936877102</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1344118442793651</v>
+        <v>0.7078909101087945</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.03215402364730835</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.3660552936877102</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1344121625450498</v>
+        <v>0.7078912283744792</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.01889414340257645</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.3660552936877102</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1344119826557497</v>
+        <v>0.7078910484851789</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.02499544620513916</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.008547846991049</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.134412024168665</v>
+        <v>0.7078910899980944</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.03033624589443207</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.008547846991049</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1344118373605458</v>
+        <v>0.7078909031899751</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.03880694508552551</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.208547846991049</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1344119065487382</v>
+        <v>0.7078909723781676</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.03382671624422073</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.208547846991049</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1344117059029804</v>
+        <v>0.7078907717324097</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.05675210058689117</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.208547846991049</v>
+        <v>0.7900000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1344117474158958</v>
+        <v>0.7078908132453251</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
+        <v>0.04687363654375076</v>
+      </c>
+      <c r="JB126" t="n">
         <v>1</v>
       </c>
-      <c r="JB126" t="n">
-        <v>1.208547846991049</v>
-      </c>
       <c r="JC126" t="n">
-        <v>0.1344117750911727</v>
+        <v>0.7078908409206019</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_1_000006.xlsx
+++ b/out/Attention-mamba2_repeat_1_000006.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.1368551254272461</v>
+        <v>-0.1368599981069565</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.1374592334032059</v>
+        <v>-0.1374639570713043</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.1638771295547485</v>
+        <v>-0.1638819575309753</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.2221213132143021</v>
+        <v>-0.2221264392137527</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.1454996913671494</v>
+        <v>-0.1455046236515045</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.8599999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.1779671162366867</v>
+        <v>-0.1779722571372986</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.8599999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.06639079749584198</v>
+        <v>-0.06639494001865387</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.8599999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.1937233954668045</v>
+        <v>-0.1937280893325806</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.8599999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.2017845958471298</v>
+        <v>-0.2017892748117447</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.8599999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.1319743692874908</v>
+        <v>-0.1319788694381714</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.1199999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.07692889869213104</v>
+        <v>-0.0769331082701683</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.1199999999999999</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.03562032803893089</v>
+        <v>-0.03562413528561592</v>
       </c>
       <c r="JB13" t="n">
         <v>0.1600000000000001</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.1020895838737488</v>
+        <v>-0.1020937860012054</v>
       </c>
       <c r="JB14" t="n">
         <v>0.4399999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.04797064885497093</v>
+        <v>-0.04797466099262238</v>
       </c>
       <c r="JB15" t="n">
         <v>0.7199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.04467331245541573</v>
+        <v>-0.04467709362506866</v>
       </c>
       <c r="JB16" t="n">
         <v>0.5799999999999998</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.0409458763897419</v>
+        <v>-0.0409495122730732</v>
       </c>
       <c r="JB17" t="n">
         <v>0.7199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.06864552944898605</v>
+        <v>-0.06864945590496063</v>
       </c>
       <c r="JB18" t="n">
         <v>0.4399999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.1061566174030304</v>
+        <v>-0.1061607226729393</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.2107341289520264</v>
+        <v>-0.2107387781143188</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.4399999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.1020998135209084</v>
+        <v>-0.1021040230989456</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.3</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.09389030933380127</v>
+        <v>-0.09389449656009674</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.16</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.04673570394515991</v>
+        <v>-0.04673950001597404</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.16</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.0547872930765152</v>
+        <v>-0.05479099601507187</v>
       </c>
       <c r="JB24" t="n">
         <v>0.5799999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.1563673913478851</v>
+        <v>-0.156371995806694</v>
       </c>
       <c r="JB25" t="n">
         <v>0.4399999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.06013930588960648</v>
+        <v>-0.06014323607087135</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.4399999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.2194398790597916</v>
+        <v>-0.2194438725709915</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.7199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.5581631064414978</v>
+        <v>-0.5581666827201843</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.7199999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.4216891229152679</v>
+        <v>-0.4216932654380798</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.9999999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.2161143869161606</v>
+        <v>-0.2161188572645187</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.7199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.1971127986907959</v>
+        <v>-0.1971175819635391</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.4399999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.07239572703838348</v>
+        <v>-0.07239991426467896</v>
       </c>
       <c r="JB32" t="n">
         <v>0.4399999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.0360049307346344</v>
+        <v>-0.03600854426622391</v>
       </c>
       <c r="JB33" t="n">
         <v>0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.06221456080675125</v>
+        <v>-0.062216617166996</v>
       </c>
       <c r="JB34" t="n">
         <v>0.4399999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.4693469107151031</v>
+        <v>-0.4693511128425598</v>
       </c>
       <c r="JB35" t="n">
         <v>0.16</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.2300769537687302</v>
+        <v>-0.2300812602043152</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.1199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.1986175030469894</v>
+        <v>-0.1986218243837357</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.8599999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.3091815114021301</v>
+        <v>-0.3091863989830017</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.8599999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.1165608540177345</v>
+        <v>-0.1165652275085449</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.8599999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.1853837072849274</v>
+        <v>-0.185387909412384</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.8599999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.4154267013072968</v>
+        <v>-0.4154307842254639</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.8599999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.6120970845222473</v>
+        <v>-0.6121007204055786</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.5395327210426331</v>
+        <v>-0.5395316481590271</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.9999999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.3282089829444885</v>
+        <v>-0.3282070755958557</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.2262930423021317</v>
+        <v>-0.2262897789478302</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37507,17 +37507,17 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.2573507726192474</v>
+        <v>-0.2573475241661072</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.9999999999999998</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>-1.081674193765502e-05</v>
       </c>
     </row>
     <row r="47">
@@ -38298,21 +38298,21 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0</v>
+        <v>-0.0299079016844244</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.3160260915756226</v>
+        <v>-0.3160236179828644</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.1199999999999999</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>-0.02991871842636203</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.2320465445518494</v>
+        <v>-0.2320439964532852</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.16</v>
+        <v>0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.0001134836890086299</v>
+        <v>-0.03004025204165862</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.3486462734059427</v>
+        <v>0.3733773879144212</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.01053029671311378</v>
+        <v>-0.01052941009402275</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.6978736245261032</v>
+        <v>0.717458330619749</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.06670953599077314</v>
+        <v>0.07144155609033796</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.09699477255344391</v>
+        <v>-0.09699326008558273</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4821374414511765</v>
+        <v>0.4864189830138113</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1168480788927817</v>
+        <v>0.125136660872915</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.04654038324952126</v>
+        <v>-0.04653874784708023</v>
       </c>
       <c r="JB51" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.6491570750943663</v>
+        <v>0.6652860801175656</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.06399049843487115</v>
+        <v>0.06852938929164064</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.07642298191785812</v>
+        <v>-0.07642150670289993</v>
       </c>
       <c r="JB52" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6601888416391501</v>
+        <v>0.6771003791001495</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.02642900776561955</v>
+        <v>0.02830383260197845</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.02751102298498154</v>
+        <v>0.02740567550063133</v>
       </c>
       <c r="JB53" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6489892767460235</v>
+        <v>0.6651063378269692</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.03292778527124096</v>
+        <v>0.03526414655080057</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.01615172997117043</v>
+        <v>-0.01615089178085327</v>
       </c>
       <c r="JB54" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.6884212571697563</v>
+        <v>0.7073355489981673</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.01982737068570714</v>
+        <v>0.02123298078436027</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.009855702519416809</v>
+        <v>0.009855948388576508</v>
       </c>
       <c r="JB55" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6951248869962326</v>
+        <v>0.7145146159468405</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.01507392729345747</v>
+        <v>0.01614277342123019</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.01748639345169067</v>
+        <v>0.01748668029904366</v>
       </c>
       <c r="JB56" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.7054371030044824</v>
+        <v>0.7255587246674141</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.006663669507098629</v>
+        <v>0.007137278542636139</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.05911973863840103</v>
+        <v>0.05911777913570404</v>
       </c>
       <c r="JB57" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.7036814689519501</v>
+        <v>0.7236787752923339</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.005286600384206369</v>
+        <v>0.005662409944381178</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.04587084427475929</v>
+        <v>0.04586918652057648</v>
       </c>
       <c r="JB58" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.7075900135154941</v>
+        <v>0.7278651935298145</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.002619052796206994</v>
+        <v>0.002806663815954873</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.04805872961878777</v>
+        <v>0.04805827513337135</v>
       </c>
       <c r="JB59" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.7075381599292262</v>
+        <v>0.7278100123089309</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.001522330391455509</v>
+        <v>0.001629970819043802</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.03247519582509995</v>
+        <v>0.0325782299041748</v>
       </c>
       <c r="JB60" t="n">
         <v>0.1199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7079598791512484</v>
+        <v>0.7282618050761244</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0007572105953549397</v>
+        <v>0.000812485409521901</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.0617130920290947</v>
+        <v>-0.06173598021268845</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.02000000000000007</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.7079539301476039</v>
+        <v>0.728255787251605</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.000371578909272003</v>
+        <v>0.0003974507427334383</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.03017359226942062</v>
+        <v>-0.03017306327819824</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.16</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.7079393628366827</v>
+        <v>0.728240565021207</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0002152850833415806</v>
+        <v>0.0002286356944531915</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.0329170860350132</v>
+        <v>-0.03294232860207558</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.3</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7079952798378195</v>
+        <v>0.7283006375226954</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>6.865501376107297e-05</v>
+        <v>7.311895398901677e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.01381964981555939</v>
+        <v>-0.01381970942020416</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.16</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.7079171244262832</v>
+        <v>0.7282169414387765</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>3.093265835633669e-05</v>
+        <v>3.542424065087878e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.01743665337562561</v>
+        <v>-0.01743680983781815</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.02000000000000007</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.707912535866699</v>
+        <v>0.7282123887419009</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>1.456956904086805e-05</v>
+        <v>1.701576517097656e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.004714787006378174</v>
+        <v>0.004714026581496</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.02000000000000007</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.7079109223175547</v>
+        <v>0.7282109727726362</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.004543937742710114</v>
+        <v>-0.004544392693787813</v>
       </c>
       <c r="JB67" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.7079052254562513</v>
+        <v>0.7282052759113328</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.03661102801561356</v>
+        <v>-0.03661072254180908</v>
       </c>
       <c r="JB68" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.7079029165514493</v>
+        <v>0.7282029670065309</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.005476668477058411</v>
+        <v>-0.005476743448525667</v>
       </c>
       <c r="JB69" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.7078969170178526</v>
+        <v>0.7281969674729342</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.01681473106145859</v>
+        <v>-0.01681481301784515</v>
       </c>
       <c r="JB70" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7078926744076987</v>
+        <v>0.7281927248627802</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.008164249360561371</v>
+        <v>0.008163735270500183</v>
       </c>
       <c r="JB71" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7078929027287334</v>
+        <v>0.7281929531838148</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.005340218544006348</v>
+        <v>-0.00534064369276166</v>
       </c>
       <c r="JB72" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7078929926733833</v>
+        <v>0.7281930431284649</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.004920072853565216</v>
+        <v>0.004919334780424833</v>
       </c>
       <c r="JB73" t="n">
         <v>0.5799999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.7078921347397985</v>
+        <v>0.72819218519488</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.02400253713130951</v>
+        <v>-0.02400257438421249</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.02000000000000007</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.7078923630608331</v>
+        <v>0.7281924135159147</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.02922547608613968</v>
+        <v>-0.02922548353672028</v>
       </c>
       <c r="JB75" t="n">
         <v>0.1199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.7078915673966214</v>
+        <v>0.7281916178517029</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.01793196797370911</v>
+        <v>0.0179310068488121</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.02000000000000007</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.7078916296659945</v>
+        <v>0.728191680121076</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.01214399188756943</v>
+        <v>0.01214312016963959</v>
       </c>
       <c r="JB77" t="n">
         <v>0.1199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.7078916573412714</v>
+        <v>0.7281917077963529</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.002599172294139862</v>
+        <v>-0.002599686849862337</v>
       </c>
       <c r="JB78" t="n">
         <v>0.2599999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7078918095552947</v>
+        <v>0.7281918600103762</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.01746876537799835</v>
+        <v>0.01746790856122971</v>
       </c>
       <c r="JB79" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.707891463614333</v>
+        <v>0.7281915140694145</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.01904160529375076</v>
+        <v>0.01904051750898361</v>
       </c>
       <c r="JB80" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.7078915397213446</v>
+        <v>0.7281915901764261</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.02050766348838806</v>
+        <v>0.02050632238388062</v>
       </c>
       <c r="JB81" t="n">
         <v>0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7078917057730062</v>
+        <v>0.7281917562280877</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.006058566272258759</v>
+        <v>0.006057917606085539</v>
       </c>
       <c r="JB82" t="n">
         <v>-0.3</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.7078920655516062</v>
+        <v>0.7281921160066878</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.01457304507493973</v>
+        <v>-0.01457338035106659</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.707892086308064</v>
+        <v>0.7281921367631454</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.01799774914979935</v>
+        <v>-0.01799771934747696</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.7078921900903524</v>
+        <v>0.728192240545434</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.01617438346147537</v>
+        <v>0.01617338508367538</v>
       </c>
       <c r="JB85" t="n">
         <v>-0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7078924184113872</v>
+        <v>0.7281924688664686</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.02054236829280853</v>
+        <v>0.02054109424352646</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.707892293872641</v>
+        <v>0.7281923443277224</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.04445857554674149</v>
+        <v>0.04437398910522461</v>
       </c>
       <c r="JB87" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.7078923215479178</v>
+        <v>0.7281923720029992</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.009290814399719238</v>
+        <v>0.009289905428886414</v>
       </c>
       <c r="JB88" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.7078923768984717</v>
+        <v>0.7281924273535533</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.01537223905324936</v>
+        <v>0.01537131518125534</v>
       </c>
       <c r="JB89" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.7078926398136024</v>
+        <v>0.7281926902686839</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.01627351343631744</v>
+        <v>0.01627237349748611</v>
       </c>
       <c r="JB90" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7078925567877716</v>
+        <v>0.7281926072428532</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.01941335946321487</v>
+        <v>0.01941152662038803</v>
       </c>
       <c r="JB91" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7078923492231949</v>
+        <v>0.7281923996782764</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.01986905932426453</v>
+        <v>0.01986537128686905</v>
       </c>
       <c r="JB92" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.7078923630608331</v>
+        <v>0.7281924135159147</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.02017711102962494</v>
+        <v>0.02017522603273392</v>
       </c>
       <c r="JB93" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7078925014372179</v>
+        <v>0.7281925518922995</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.02129106968641281</v>
+        <v>0.02128865569829941</v>
       </c>
       <c r="JB94" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7078922177656293</v>
+        <v>0.7281922682207108</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.04842314869165421</v>
+        <v>0.04841553419828415</v>
       </c>
       <c r="JB95" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7078920447951486</v>
+        <v>0.7281920952502301</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.02052116394042969</v>
+        <v>0.02051989734172821</v>
       </c>
       <c r="JB96" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.70789194101286</v>
+        <v>0.7281919914679416</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.02212964743375778</v>
+        <v>0.02212750911712646</v>
       </c>
       <c r="JB97" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.707892086308064</v>
+        <v>0.7281921367631454</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.04404269903898239</v>
+        <v>0.04395650327205658</v>
       </c>
       <c r="JB98" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7078923284667372</v>
+        <v>0.7281923789218187</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.02440916001796722</v>
+        <v>0.02440763264894485</v>
       </c>
       <c r="JB99" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.7078921554962562</v>
+        <v>0.7281922059513377</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.04737485945224762</v>
+        <v>0.04737302660942078</v>
       </c>
       <c r="JB100" t="n">
         <v>0.2599999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.7078918579870292</v>
+        <v>0.7281919084421108</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.02588031440973282</v>
+        <v>0.02587889134883881</v>
       </c>
       <c r="JB101" t="n">
         <v>0.1199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7078918441493907</v>
+        <v>0.7281918946044722</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.05062063038349152</v>
+        <v>0.05061756074428558</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.02000000000000007</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7078914774519715</v>
+        <v>0.728191527907053</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.02063741534948349</v>
+        <v>0.02063353359699249</v>
       </c>
       <c r="JB103" t="n">
         <v>0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.7078914774519715</v>
+        <v>0.728191527907053</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.01149188727140427</v>
+        <v>0.01149113476276398</v>
       </c>
       <c r="JB104" t="n">
         <v>0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.7078914151825983</v>
+        <v>0.7281914656376799</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.0496564656496048</v>
+        <v>0.0495256781578064</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.02000000000000007</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.7078913114003099</v>
+        <v>0.7281913618553915</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.03551651537418365</v>
+        <v>0.03540109843015671</v>
       </c>
       <c r="JB106" t="n">
         <v>0.1199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7078911384298292</v>
+        <v>0.7281911888849106</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.0306030735373497</v>
+        <v>0.03060177713632584</v>
       </c>
       <c r="JB107" t="n">
         <v>0.2599999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.7078911868615637</v>
+        <v>0.7281912373166453</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.03239016234874725</v>
+        <v>0.03235388547182083</v>
       </c>
       <c r="JB108" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7078908270829637</v>
+        <v>0.7281908775380451</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.05111902952194214</v>
+        <v>0.05111730843782425</v>
       </c>
       <c r="JB109" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.7078907855700483</v>
+        <v>0.7281908360251298</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.03704218566417694</v>
+        <v>0.03704075515270233</v>
       </c>
       <c r="JB110" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7078908409206019</v>
+        <v>0.7281908913756835</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.04967382550239563</v>
+        <v>0.04967197775840759</v>
       </c>
       <c r="JB111" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.7078908962711559</v>
+        <v>0.7281909467262374</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.05203325301408768</v>
+        <v>0.05203128606081009</v>
       </c>
       <c r="JB112" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.7078909377840713</v>
+        <v>0.7281909882391528</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.04724203050136566</v>
+        <v>0.04724015295505524</v>
       </c>
       <c r="JB113" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7078906679501212</v>
+        <v>0.7281907184052028</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.04793474078178406</v>
+        <v>0.04793290048837662</v>
       </c>
       <c r="JB114" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.7078907233006752</v>
+        <v>0.7281907737557567</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.04894070327281952</v>
+        <v>0.04893882572650909</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.02000000000000007</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.707890868595879</v>
+        <v>0.7281909190509606</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.04723411053419113</v>
+        <v>0.04723229259252548</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3</v>
+        <v>-0.16</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.7078908340017828</v>
+        <v>0.7281908844568643</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.04628936201334</v>
+        <v>0.04628759622573853</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.7078908201641443</v>
+        <v>0.7281908706192258</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.02758223563432693</v>
+        <v>0.02758120000362396</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.7078909101087945</v>
+        <v>0.728190960563876</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.03215402364730835</v>
+        <v>-0.03215403109788895</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7078912283744792</v>
+        <v>0.7281912788295606</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.01889414340257645</v>
+        <v>0.01889332383871078</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7078910484851789</v>
+        <v>0.7281910989402605</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.02499544620513916</v>
+        <v>0.02499420195817947</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.7199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7078910899980944</v>
+        <v>0.7281911404531759</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.03033624589443207</v>
+        <v>0.03033483028411865</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7078909031899751</v>
+        <v>0.7281909536450566</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.03880694508552551</v>
+        <v>0.03869420289993286</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7078909723781676</v>
+        <v>0.7281910228332491</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.03382671624422073</v>
+        <v>0.03382532298564911</v>
       </c>
       <c r="JB124" t="n">
         <v>0.5799999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7078907717324097</v>
+        <v>0.7281908221874912</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.05675210058689117</v>
+        <v>0.05675005167722702</v>
       </c>
       <c r="JB125" t="n">
         <v>0.7900000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7078908132453251</v>
+        <v>0.7281908637004066</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.04687363654375076</v>
+        <v>0.04687092453241348</v>
       </c>
       <c r="JB126" t="n">
         <v>1</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7078908409206019</v>
+        <v>0.7281908913756835</v>
       </c>
     </row>
   </sheetData>
